--- a/mapping/fixtures/excel_handmade.xlsx
+++ b/mapping/fixtures/excel_handmade.xlsx
@@ -626,7 +626,7 @@
         <v>0.19</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>357.74</v>
+        <v>357.75</v>
       </c>
     </row>
   </sheetData>
